--- a/data/dividends_info_20260425.xlsx
+++ b/data/dividends_info_20260425.xlsx
@@ -9372,7 +9372,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9382,7 +9382,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9406,7 +9406,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9491,7 +9491,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9831,7 +9831,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10001,7 +10001,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10035,7 +10035,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10045,14 +10045,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10069,7 +10069,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10086,7 +10086,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10103,7 +10103,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10120,7 +10120,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10137,7 +10137,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10171,7 +10171,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10181,14 +10181,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10205,7 +10205,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10222,7 +10222,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10256,7 +10256,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10266,14 +10266,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10290,7 +10290,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10307,7 +10307,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10324,7 +10324,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10341,7 +10341,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10358,7 +10358,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10368,14 +10368,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10392,7 +10392,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10409,7 +10409,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10426,7 +10426,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10436,14 +10436,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10460,7 +10460,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10477,7 +10477,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10494,7 +10494,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10504,14 +10504,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10521,14 +10521,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10538,14 +10538,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10555,14 +10555,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10579,7 +10579,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10596,7 +10596,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10613,7 +10613,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10630,7 +10630,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10647,7 +10647,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10664,7 +10664,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10681,7 +10681,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10698,7 +10698,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10715,7 +10715,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10732,7 +10732,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10749,7 +10749,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10766,7 +10766,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10783,7 +10783,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10800,7 +10800,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10817,7 +10817,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10834,7 +10834,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10851,7 +10851,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10885,7 +10885,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10902,7 +10902,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10919,7 +10919,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10946,14 +10946,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10970,7 +10970,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10987,7 +10987,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11004,7 +11004,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11014,14 +11014,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11038,7 +11038,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11055,7 +11055,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11065,14 +11065,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11089,7 +11089,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11106,7 +11106,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11123,7 +11123,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11140,7 +11140,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11157,7 +11157,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11174,7 +11174,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11184,14 +11184,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11208,7 +11208,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11218,14 +11218,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11235,14 +11235,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11259,7 +11259,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11269,14 +11269,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11293,7 +11293,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11310,7 +11310,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11327,7 +11327,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11337,14 +11337,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11361,7 +11361,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11378,7 +11378,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11395,7 +11395,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11405,14 +11405,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11429,7 +11429,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11439,14 +11439,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11456,14 +11456,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11480,7 +11480,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11490,14 +11490,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11507,14 +11507,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11524,14 +11524,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11548,7 +11548,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11565,7 +11565,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11599,7 +11599,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11616,7 +11616,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11626,14 +11626,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11650,7 +11650,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11667,7 +11667,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11684,7 +11684,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11701,7 +11701,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11711,14 +11711,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11735,7 +11735,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11745,14 +11745,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11769,7 +11769,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11786,7 +11786,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11796,14 +11796,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11820,7 +11820,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11837,7 +11837,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11847,14 +11847,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11864,14 +11864,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11888,7 +11888,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11905,7 +11905,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11922,7 +11922,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11939,7 +11939,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11956,7 +11956,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11973,7 +11973,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11990,7 +11990,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12007,7 +12007,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12017,14 +12017,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12041,7 +12041,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12058,7 +12058,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12075,7 +12075,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12092,7 +12092,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12109,7 +12109,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12126,7 +12126,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12160,7 +12160,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12177,7 +12177,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12187,14 +12187,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12296,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12313,7 +12313,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12330,7 +12330,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12347,7 +12347,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12364,7 +12364,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12381,7 +12381,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12398,7 +12398,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12415,7 +12415,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12432,7 +12432,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12449,7 +12449,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12459,14 +12459,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12483,7 +12483,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12500,7 +12500,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12517,7 +12517,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12527,14 +12527,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12551,7 +12551,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12568,7 +12568,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12585,7 +12585,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12602,7 +12602,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12619,7 +12619,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12636,7 +12636,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12653,7 +12653,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12663,14 +12663,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12687,7 +12687,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12704,7 +12704,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12721,7 +12721,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12731,14 +12731,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12755,7 +12755,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12772,7 +12772,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12789,7 +12789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12823,7 +12823,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12840,7 +12840,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12857,7 +12857,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12891,7 +12891,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12908,7 +12908,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12925,7 +12925,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12935,14 +12935,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12959,7 +12959,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12969,14 +12969,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12993,7 +12993,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13003,14 +13003,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13027,7 +13027,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13044,7 +13044,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13054,14 +13054,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13071,14 +13071,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13095,7 +13095,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13105,14 +13105,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13122,14 +13122,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13146,7 +13146,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13180,7 +13180,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13190,14 +13190,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13231,7 +13231,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13241,14 +13241,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13282,7 +13282,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13299,7 +13299,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13309,14 +13309,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13333,7 +13333,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13350,7 +13350,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13360,14 +13360,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13377,14 +13377,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13401,7 +13401,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13418,7 +13418,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13435,7 +13435,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13445,14 +13445,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13462,14 +13462,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13479,14 +13479,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13503,7 +13503,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13520,7 +13520,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13530,14 +13530,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13571,7 +13571,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13581,14 +13581,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13598,14 +13598,14 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13615,14 +13615,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13632,14 +13632,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13683,14 +13683,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13707,7 +13707,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13768,14 +13768,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13792,7 +13792,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13802,14 +13802,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13819,14 +13819,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13836,14 +13836,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13860,7 +13860,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13870,14 +13870,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13887,14 +13887,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13904,14 +13904,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13921,14 +13921,14 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13955,14 +13955,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13972,14 +13972,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13989,14 +13989,14 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14040,14 +14040,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14057,14 +14057,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14081,7 +14081,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14091,14 +14091,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14108,14 +14108,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14125,14 +14125,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14149,7 +14149,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14166,7 +14166,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14176,7 +14176,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -14200,7 +14200,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14210,14 +14210,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14234,7 +14234,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14244,14 +14244,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14268,7 +14268,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14278,14 +14278,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14295,14 +14295,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14319,7 +14319,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14329,14 +14329,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14353,7 +14353,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14363,14 +14363,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14380,14 +14380,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14404,7 +14404,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14414,14 +14414,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14431,14 +14431,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14455,7 +14455,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14465,14 +14465,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14489,7 +14489,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14499,14 +14499,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14516,14 +14516,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14533,14 +14533,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14550,14 +14550,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14567,14 +14567,14 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14584,14 +14584,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14608,7 +14608,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14625,7 +14625,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14642,7 +14642,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14659,7 +14659,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14676,7 +14676,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14686,14 +14686,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14703,14 +14703,14 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14727,7 +14727,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14744,7 +14744,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -14778,7 +14778,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14795,7 +14795,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14805,14 +14805,14 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14829,7 +14829,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14846,7 +14846,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14856,14 +14856,14 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14880,7 +14880,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14890,14 +14890,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14907,14 +14907,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14931,7 +14931,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14941,14 +14941,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14965,7 +14965,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14982,7 +14982,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14992,14 +14992,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15009,14 +15009,14 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -15026,14 +15026,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15043,14 +15043,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15060,14 +15060,14 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -15077,14 +15077,14 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15094,14 +15094,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15111,14 +15111,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15128,14 +15128,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15145,14 +15145,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15162,14 +15162,14 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15179,14 +15179,14 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15196,14 +15196,14 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15220,7 +15220,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15230,14 +15230,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15254,7 +15254,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15264,14 +15264,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15288,7 +15288,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15305,7 +15305,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15315,14 +15315,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -15373,7 +15373,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15390,7 +15390,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15400,14 +15400,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15424,7 +15424,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15441,7 +15441,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15458,7 +15458,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15475,7 +15475,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15492,7 +15492,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15502,14 +15502,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15526,7 +15526,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15560,7 +15560,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15570,14 +15570,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15587,14 +15587,14 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15604,14 +15604,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15621,14 +15621,14 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15645,7 +15645,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15655,14 +15655,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15672,14 +15672,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15696,7 +15696,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15706,7 +15706,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15730,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15747,7 +15747,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15764,7 +15764,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15781,7 +15781,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15798,7 +15798,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15815,7 +15815,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15825,14 +15825,14 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15842,14 +15842,14 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15866,7 +15866,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15876,14 +15876,14 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -15893,14 +15893,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15917,7 +15917,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15927,14 +15927,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15951,7 +15951,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15961,14 +15961,14 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15985,7 +15985,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -16002,7 +16002,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -16019,7 +16019,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -16036,7 +16036,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -16053,7 +16053,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16063,14 +16063,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16087,7 +16087,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -16097,14 +16097,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16114,14 +16114,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16138,7 +16138,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16155,7 +16155,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16165,14 +16165,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16182,14 +16182,14 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16199,14 +16199,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16216,14 +16216,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16240,7 +16240,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16257,7 +16257,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16267,14 +16267,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16291,7 +16291,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16308,7 +16308,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16325,7 +16325,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16335,14 +16335,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16352,14 +16352,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16376,7 +16376,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16393,7 +16393,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16410,7 +16410,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16427,7 +16427,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16444,7 +16444,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16454,14 +16454,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16478,7 +16478,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16495,7 +16495,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16512,7 +16512,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16529,7 +16529,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16556,14 +16556,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16580,7 +16580,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16590,14 +16590,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16607,14 +16607,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16631,7 +16631,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16648,7 +16648,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16665,7 +16665,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16682,7 +16682,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16692,14 +16692,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16716,7 +16716,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16726,14 +16726,14 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16750,7 +16750,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16767,7 +16767,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16784,7 +16784,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16801,7 +16801,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16818,7 +16818,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16835,7 +16835,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16845,14 +16845,14 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16869,7 +16869,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16886,7 +16886,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16903,7 +16903,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16920,7 +16920,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16947,7 +16947,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -16964,14 +16964,14 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16988,7 +16988,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -17005,7 +17005,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -17015,14 +17015,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -17032,14 +17032,14 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -17056,7 +17056,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -17066,14 +17066,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -17090,7 +17090,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -17100,14 +17100,14 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -17124,7 +17124,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17141,7 +17141,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17158,7 +17158,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17175,7 +17175,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17185,14 +17185,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17209,7 +17209,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17226,7 +17226,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17243,7 +17243,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17260,7 +17260,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17270,14 +17270,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17287,14 +17287,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17311,7 +17311,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17321,14 +17321,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17338,14 +17338,14 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17362,7 +17362,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17372,14 +17372,14 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17389,14 +17389,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17413,7 +17413,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17430,7 +17430,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17447,7 +17447,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17464,7 +17464,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17474,14 +17474,14 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17508,14 +17508,14 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17525,14 +17525,14 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17542,14 +17542,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17566,7 +17566,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17583,7 +17583,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -17593,14 +17593,14 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17617,7 +17617,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17634,7 +17634,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17651,7 +17651,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17661,14 +17661,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17678,14 +17678,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17702,7 +17702,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17712,14 +17712,14 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17729,14 +17729,14 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17746,14 +17746,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17763,14 +17763,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17780,14 +17780,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17804,7 +17804,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17821,7 +17821,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17831,14 +17831,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17848,14 +17848,14 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17872,7 +17872,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17889,7 +17889,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17899,14 +17899,14 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17916,14 +17916,14 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17933,14 +17933,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17950,14 +17950,14 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17967,14 +17967,14 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17984,14 +17984,14 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -18001,14 +18001,14 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -18018,14 +18018,14 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -18035,14 +18035,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -18052,14 +18052,14 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -18069,14 +18069,14 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18086,14 +18086,14 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -18103,14 +18103,14 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -18120,14 +18120,14 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -18161,7 +18161,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -18171,14 +18171,14 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18188,14 +18188,14 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18212,7 +18212,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18222,14 +18222,14 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18246,7 +18246,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18256,14 +18256,14 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18273,14 +18273,14 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18365,7 +18365,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18382,7 +18382,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18399,7 +18399,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18409,14 +18409,14 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18426,14 +18426,14 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18450,7 +18450,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18460,14 +18460,14 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18477,7 +18477,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18505,146 +18505,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>COFLE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DBA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>E-NOVIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Indel B S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MEVIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sicily by Car S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Vivenda Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>